--- a/backend/data/financials_by_company/1692.HK.xlsx
+++ b/backend/data/financials_by_company/1692.HK.xlsx
@@ -652,59 +652,57 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-567652.391943</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.174878</v>
+        <v>0.153817</v>
       </c>
       <c r="D2" t="n">
-        <v>167017000</v>
+        <v>152550000</v>
       </c>
       <c r="E2" t="n">
-        <v>-3246000</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-3246000</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>107610000</v>
+        <v>106504000</v>
       </c>
       <c r="H2" t="n">
-        <v>31042000</v>
+        <v>25846000</v>
       </c>
       <c r="I2" t="n">
-        <v>471844000</v>
+        <v>542097000</v>
       </c>
       <c r="J2" t="n">
-        <v>163771000</v>
+        <v>152550000</v>
       </c>
       <c r="K2" t="n">
-        <v>132729000</v>
+        <v>126704000</v>
       </c>
       <c r="L2" t="n">
-        <v>2431000</v>
+        <v>396000</v>
       </c>
       <c r="M2" t="n">
-        <v>2312000</v>
+        <v>840000</v>
       </c>
       <c r="N2" t="n">
-        <v>4743000</v>
+        <v>1236000</v>
       </c>
       <c r="O2" t="n">
-        <v>110288347.608057</v>
+        <v>106504000</v>
       </c>
       <c r="P2" t="n">
-        <v>107610000</v>
+        <v>106504000</v>
       </c>
       <c r="Q2" t="n">
-        <v>585260000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>20000</v>
-      </c>
+        <v>640354000</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>359000000</v>
       </c>
@@ -712,139 +710,133 @@
         <v>359000000</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2997</v>
+        <v>0.2967</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2997</v>
+        <v>0.2967</v>
       </c>
       <c r="W2" t="n">
-        <v>107610000</v>
+        <v>106504000</v>
       </c>
       <c r="X2" t="n">
-        <v>107610000</v>
+        <v>106504000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>107610000</v>
+        <v>106504000</v>
       </c>
       <c r="AA2" t="n">
-        <v>107610000</v>
+        <v>106504000</v>
       </c>
       <c r="AB2" t="n">
-        <v>107610000</v>
+        <v>106504000</v>
       </c>
       <c r="AC2" t="n">
-        <v>22807000</v>
+        <v>19360000</v>
       </c>
       <c r="AD2" t="n">
-        <v>130417000</v>
+        <v>125864000</v>
       </c>
       <c r="AE2" t="n">
-        <v>7670000</v>
+        <v>2238000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-3246000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>42000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>3204000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>2431000</v>
+        <v>396000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2312000</v>
+        <v>840000</v>
       </c>
       <c r="AK2" t="n">
-        <v>4743000</v>
+        <v>1236000</v>
       </c>
       <c r="AL2" t="n">
-        <v>118333000</v>
+        <v>122731000</v>
       </c>
       <c r="AM2" t="n">
-        <v>113416000</v>
+        <v>98257000</v>
       </c>
       <c r="AN2" t="n">
-        <v>114420000</v>
+        <v>99163000</v>
       </c>
       <c r="AO2" t="n">
-        <v>15588000</v>
+        <v>14648000</v>
       </c>
       <c r="AP2" t="n">
-        <v>98832000</v>
+        <v>84515000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>231749000</v>
+        <v>220988000</v>
       </c>
       <c r="AR2" t="n">
-        <v>471844000</v>
+        <v>542097000</v>
       </c>
       <c r="AS2" t="n">
-        <v>703593000</v>
+        <v>763085000</v>
       </c>
       <c r="AT2" t="n">
-        <v>703593000</v>
+        <v>763085000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>113601.567185</v>
+        <v>668</v>
       </c>
       <c r="C3" t="n">
-        <v>0.167307</v>
+        <v>0.167</v>
       </c>
       <c r="D3" t="n">
-        <v>177403000</v>
+        <v>192917000</v>
       </c>
       <c r="E3" t="n">
-        <v>679000</v>
+        <v>4000</v>
       </c>
       <c r="F3" t="n">
-        <v>679000</v>
+        <v>4000</v>
       </c>
       <c r="G3" t="n">
-        <v>122206000</v>
+        <v>134311000</v>
       </c>
       <c r="H3" t="n">
-        <v>28735000</v>
+        <v>27918000</v>
       </c>
       <c r="I3" t="n">
-        <v>459042000</v>
+        <v>561198000</v>
       </c>
       <c r="J3" t="n">
-        <v>178082000</v>
+        <v>192921000</v>
       </c>
       <c r="K3" t="n">
-        <v>149347000</v>
+        <v>165003000</v>
       </c>
       <c r="L3" t="n">
-        <v>3545000</v>
+        <v>-3095000</v>
       </c>
       <c r="M3" t="n">
-        <v>2587000</v>
+        <v>3972000</v>
       </c>
       <c r="N3" t="n">
-        <v>6132000</v>
+        <v>877000</v>
       </c>
       <c r="O3" t="n">
-        <v>121640601.567185</v>
+        <v>134307668</v>
       </c>
       <c r="P3" t="n">
-        <v>122206000</v>
+        <v>134311000</v>
       </c>
       <c r="Q3" t="n">
-        <v>570085000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>39000</v>
-      </c>
+        <v>665179000</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
         <v>359000000</v>
       </c>
@@ -852,137 +844,137 @@
         <v>359000000</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3404</v>
+        <v>0.3741</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3404</v>
+        <v>0.3741</v>
       </c>
       <c r="W3" t="n">
-        <v>122206000</v>
+        <v>134311000</v>
       </c>
       <c r="X3" t="n">
-        <v>122206000</v>
+        <v>134311000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>122206000</v>
+        <v>134311000</v>
       </c>
       <c r="AA3" t="n">
-        <v>122206000</v>
+        <v>134311000</v>
       </c>
       <c r="AB3" t="n">
-        <v>122206000</v>
+        <v>134311000</v>
       </c>
       <c r="AC3" t="n">
-        <v>24554000</v>
+        <v>26720000</v>
       </c>
       <c r="AD3" t="n">
-        <v>146760000</v>
+        <v>161031000</v>
       </c>
       <c r="AE3" t="n">
-        <v>5484000</v>
+        <v>308000</v>
       </c>
       <c r="AF3" t="n">
-        <v>679000</v>
+        <v>4000</v>
       </c>
       <c r="AG3" t="n">
-        <v>15000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-694000</v>
-      </c>
+        <v>-4000</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>3545000</v>
+        <v>-3095000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2587000</v>
+        <v>3972000</v>
       </c>
       <c r="AK3" t="n">
-        <v>6132000</v>
+        <v>877000</v>
       </c>
       <c r="AL3" t="n">
-        <v>134332000</v>
+        <v>158479000</v>
       </c>
       <c r="AM3" t="n">
-        <v>111043000</v>
+        <v>103981000</v>
       </c>
       <c r="AN3" t="n">
-        <v>111178000</v>
+        <v>106880000</v>
       </c>
       <c r="AO3" t="n">
-        <v>17213000</v>
+        <v>15035000</v>
       </c>
       <c r="AP3" t="n">
-        <v>93965000</v>
+        <v>91845000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>245375000</v>
+        <v>262460000</v>
       </c>
       <c r="AR3" t="n">
-        <v>459042000</v>
+        <v>561198000</v>
       </c>
       <c r="AS3" t="n">
-        <v>704417000</v>
+        <v>823658000</v>
       </c>
       <c r="AT3" t="n">
-        <v>704417000</v>
+        <v>823658000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>668</v>
+        <v>113601.567185</v>
       </c>
       <c r="C4" t="n">
-        <v>0.167</v>
+        <v>0.167307</v>
       </c>
       <c r="D4" t="n">
-        <v>192917000</v>
+        <v>177403000</v>
       </c>
       <c r="E4" t="n">
-        <v>4000</v>
+        <v>679000</v>
       </c>
       <c r="F4" t="n">
-        <v>4000</v>
+        <v>679000</v>
       </c>
       <c r="G4" t="n">
-        <v>134311000</v>
+        <v>122206000</v>
       </c>
       <c r="H4" t="n">
-        <v>27918000</v>
+        <v>28735000</v>
       </c>
       <c r="I4" t="n">
-        <v>561198000</v>
+        <v>459042000</v>
       </c>
       <c r="J4" t="n">
-        <v>192921000</v>
+        <v>178082000</v>
       </c>
       <c r="K4" t="n">
-        <v>165003000</v>
+        <v>149347000</v>
       </c>
       <c r="L4" t="n">
-        <v>-3095000</v>
+        <v>3545000</v>
       </c>
       <c r="M4" t="n">
-        <v>3972000</v>
+        <v>2587000</v>
       </c>
       <c r="N4" t="n">
-        <v>877000</v>
+        <v>6132000</v>
       </c>
       <c r="O4" t="n">
-        <v>134307668</v>
+        <v>121640601.567185</v>
       </c>
       <c r="P4" t="n">
-        <v>134311000</v>
+        <v>122206000</v>
       </c>
       <c r="Q4" t="n">
-        <v>665179000</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
+        <v>570085000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>39000</v>
+      </c>
       <c r="S4" t="n">
         <v>359000000</v>
       </c>
@@ -990,135 +982,139 @@
         <v>359000000</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3741</v>
+        <v>0.3404</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3741</v>
+        <v>0.3404</v>
       </c>
       <c r="W4" t="n">
-        <v>134311000</v>
+        <v>122206000</v>
       </c>
       <c r="X4" t="n">
-        <v>134311000</v>
+        <v>122206000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>134311000</v>
+        <v>122206000</v>
       </c>
       <c r="AA4" t="n">
-        <v>134311000</v>
+        <v>122206000</v>
       </c>
       <c r="AB4" t="n">
-        <v>134311000</v>
+        <v>122206000</v>
       </c>
       <c r="AC4" t="n">
-        <v>26720000</v>
+        <v>24554000</v>
       </c>
       <c r="AD4" t="n">
-        <v>161031000</v>
+        <v>146760000</v>
       </c>
       <c r="AE4" t="n">
-        <v>308000</v>
+        <v>5484000</v>
       </c>
       <c r="AF4" t="n">
-        <v>4000</v>
+        <v>679000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-4000</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+        <v>15000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-694000</v>
+      </c>
       <c r="AI4" t="n">
-        <v>-3095000</v>
+        <v>3545000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3972000</v>
+        <v>2587000</v>
       </c>
       <c r="AK4" t="n">
-        <v>877000</v>
+        <v>6132000</v>
       </c>
       <c r="AL4" t="n">
-        <v>158479000</v>
+        <v>134332000</v>
       </c>
       <c r="AM4" t="n">
-        <v>103981000</v>
+        <v>111043000</v>
       </c>
       <c r="AN4" t="n">
-        <v>106880000</v>
+        <v>111178000</v>
       </c>
       <c r="AO4" t="n">
-        <v>15035000</v>
+        <v>17213000</v>
       </c>
       <c r="AP4" t="n">
-        <v>91845000</v>
+        <v>93965000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>262460000</v>
+        <v>245375000</v>
       </c>
       <c r="AR4" t="n">
-        <v>561198000</v>
+        <v>459042000</v>
       </c>
       <c r="AS4" t="n">
-        <v>823658000</v>
+        <v>704417000</v>
       </c>
       <c r="AT4" t="n">
-        <v>823658000</v>
+        <v>704417000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>-567652.391943</v>
       </c>
       <c r="C5" t="n">
-        <v>0.153817</v>
+        <v>0.174878</v>
       </c>
       <c r="D5" t="n">
-        <v>152550000</v>
+        <v>167017000</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-3246000</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-3246000</v>
       </c>
       <c r="G5" t="n">
-        <v>106504000</v>
+        <v>107610000</v>
       </c>
       <c r="H5" t="n">
-        <v>25846000</v>
+        <v>31042000</v>
       </c>
       <c r="I5" t="n">
-        <v>542097000</v>
+        <v>471844000</v>
       </c>
       <c r="J5" t="n">
-        <v>152550000</v>
+        <v>163771000</v>
       </c>
       <c r="K5" t="n">
-        <v>126704000</v>
+        <v>132729000</v>
       </c>
       <c r="L5" t="n">
-        <v>396000</v>
+        <v>2431000</v>
       </c>
       <c r="M5" t="n">
-        <v>840000</v>
+        <v>2312000</v>
       </c>
       <c r="N5" t="n">
-        <v>1236000</v>
+        <v>4743000</v>
       </c>
       <c r="O5" t="n">
-        <v>106504000</v>
+        <v>110288347.608057</v>
       </c>
       <c r="P5" t="n">
-        <v>106504000</v>
+        <v>107610000</v>
       </c>
       <c r="Q5" t="n">
-        <v>640354000</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>585260000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>20000</v>
+      </c>
       <c r="S5" t="n">
         <v>359000000</v>
       </c>
@@ -1126,78 +1122,82 @@
         <v>359000000</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2967</v>
+        <v>0.2997</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2967</v>
+        <v>0.2997</v>
       </c>
       <c r="W5" t="n">
-        <v>106504000</v>
+        <v>107610000</v>
       </c>
       <c r="X5" t="n">
-        <v>106504000</v>
+        <v>107610000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>106504000</v>
+        <v>107610000</v>
       </c>
       <c r="AA5" t="n">
-        <v>106504000</v>
+        <v>107610000</v>
       </c>
       <c r="AB5" t="n">
-        <v>106504000</v>
+        <v>107610000</v>
       </c>
       <c r="AC5" t="n">
-        <v>19360000</v>
+        <v>22807000</v>
       </c>
       <c r="AD5" t="n">
-        <v>125864000</v>
+        <v>130417000</v>
       </c>
       <c r="AE5" t="n">
-        <v>2238000</v>
+        <v>7670000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
+        <v>-3246000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>42000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>3204000</v>
+      </c>
       <c r="AI5" t="n">
-        <v>396000</v>
+        <v>2431000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>840000</v>
+        <v>2312000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1236000</v>
+        <v>4743000</v>
       </c>
       <c r="AL5" t="n">
-        <v>122731000</v>
+        <v>118333000</v>
       </c>
       <c r="AM5" t="n">
-        <v>98257000</v>
+        <v>113416000</v>
       </c>
       <c r="AN5" t="n">
-        <v>99163000</v>
+        <v>114420000</v>
       </c>
       <c r="AO5" t="n">
-        <v>14648000</v>
+        <v>15588000</v>
       </c>
       <c r="AP5" t="n">
-        <v>84515000</v>
+        <v>98832000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>220988000</v>
+        <v>231749000</v>
       </c>
       <c r="AR5" t="n">
-        <v>542097000</v>
+        <v>471844000</v>
       </c>
       <c r="AS5" t="n">
-        <v>763085000</v>
+        <v>703593000</v>
       </c>
       <c r="AT5" t="n">
-        <v>763085000</v>
+        <v>703593000</v>
       </c>
     </row>
   </sheetData>
@@ -1513,7 +1513,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>359000000</v>
@@ -1522,41 +1522,43 @@
         <v>359000000</v>
       </c>
       <c r="D2" t="n">
-        <v>87726000</v>
+        <v>115317000</v>
       </c>
       <c r="E2" t="n">
-        <v>355042000</v>
+        <v>332186000</v>
       </c>
       <c r="F2" t="n">
-        <v>395017000</v>
+        <v>412330000</v>
       </c>
       <c r="G2" t="n">
-        <v>170577000</v>
+        <v>253231000</v>
       </c>
       <c r="H2" t="n">
-        <v>355042000</v>
+        <v>332186000</v>
       </c>
       <c r="I2" t="n">
-        <v>47751000</v>
+        <v>35173000</v>
       </c>
       <c r="J2" t="n">
-        <v>355042000</v>
+        <v>332186000</v>
       </c>
       <c r="K2" t="n">
-        <v>355042000</v>
+        <v>332186000</v>
       </c>
       <c r="L2" t="n">
-        <v>355042000</v>
+        <v>332186000</v>
       </c>
       <c r="M2" t="n">
-        <v>355042000</v>
+        <v>332186000</v>
       </c>
       <c r="N2" t="n">
         <v>10050000</v>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
       <c r="P2" t="n">
-        <v>200351000</v>
+        <v>163967000</v>
       </c>
       <c r="Q2" t="n">
         <v>136524000</v>
@@ -1568,132 +1570,130 @@
         <v>3590000</v>
       </c>
       <c r="T2" t="n">
-        <v>199414000</v>
+        <v>276291000</v>
       </c>
       <c r="U2" t="n">
-        <v>33802000</v>
+        <v>28006000</v>
       </c>
       <c r="V2" t="n">
-        <v>220000</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1999000</v>
+        <v>5906000</v>
       </c>
       <c r="X2" t="n">
-        <v>31583000</v>
+        <v>22100000</v>
       </c>
       <c r="Y2" t="n">
-        <v>31583000</v>
+        <v>22100000</v>
       </c>
       <c r="Z2" t="n">
-        <v>165612000</v>
+        <v>248285000</v>
       </c>
       <c r="AA2" t="n">
-        <v>56143000</v>
+        <v>93217000</v>
       </c>
       <c r="AB2" t="n">
-        <v>16168000</v>
+        <v>13073000</v>
       </c>
       <c r="AC2" t="n">
-        <v>39975000</v>
+        <v>80144000</v>
       </c>
       <c r="AD2" t="n">
-        <v>61707000</v>
+        <v>94697000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1649000</v>
+        <v>653000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1604000</v>
+        <v>3471000</v>
       </c>
       <c r="AG2" t="n">
-        <v>58454000</v>
+        <v>90573000</v>
       </c>
       <c r="AH2" t="n">
-        <v>554456000</v>
+        <v>608477000</v>
       </c>
       <c r="AI2" t="n">
-        <v>218267000</v>
+        <v>106961000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>206000</v>
+        <v>65000</v>
       </c>
       <c r="AK2" t="n">
-        <v>3337000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>2200000</v>
-      </c>
+        <v>1138000</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
-        <v>212524000</v>
+        <v>105758000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-69650000</v>
+        <v>-35670000</v>
       </c>
       <c r="AO2" t="n">
-        <v>282174000</v>
+        <v>141428000</v>
       </c>
       <c r="AP2" t="n">
-        <v>11384000</v>
+        <v>18697000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>43983000</v>
+        <v>30783000</v>
       </c>
       <c r="AR2" t="n">
-        <v>65226000</v>
+        <v>49609000</v>
       </c>
       <c r="AS2" t="n">
-        <v>161581000</v>
+        <v>42339000</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>336189000</v>
+        <v>501516000</v>
       </c>
       <c r="AV2" t="n">
-        <v>820000</v>
+        <v>88000</v>
       </c>
       <c r="AW2" t="n">
-        <v>17754000</v>
+        <v>27011000</v>
       </c>
       <c r="AX2" t="n">
-        <v>100128000</v>
+        <v>206732000</v>
       </c>
       <c r="AY2" t="n">
-        <v>48285000</v>
+        <v>46071000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17213000</v>
+        <v>42421000</v>
       </c>
       <c r="BA2" t="n">
-        <v>34630000</v>
+        <v>118240000</v>
       </c>
       <c r="BB2" t="n">
-        <v>5736000</v>
+        <v>26910000</v>
       </c>
       <c r="BC2" t="n">
-        <v>153000</v>
+        <v>3683000</v>
       </c>
       <c r="BD2" t="n">
-        <v>135704000</v>
+        <v>119180000</v>
       </c>
       <c r="BE2" t="n">
-        <v>-3635000</v>
+        <v>-101000</v>
       </c>
       <c r="BF2" t="n">
-        <v>135704000</v>
+        <v>119180000</v>
       </c>
       <c r="BG2" t="n">
-        <v>75894000</v>
+        <v>144923000</v>
       </c>
       <c r="BH2" t="n">
-        <v>75894000</v>
+        <v>144923000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>359000000</v>
@@ -1702,41 +1702,41 @@
         <v>359000000</v>
       </c>
       <c r="D3" t="n">
-        <v>33887000</v>
+        <v>60443000</v>
       </c>
       <c r="E3" t="n">
-        <v>344678000</v>
+        <v>349926000</v>
       </c>
       <c r="F3" t="n">
-        <v>366064000</v>
+        <v>385681000</v>
       </c>
       <c r="G3" t="n">
-        <v>194853000</v>
+        <v>199837000</v>
       </c>
       <c r="H3" t="n">
-        <v>344678000</v>
+        <v>349926000</v>
       </c>
       <c r="I3" t="n">
-        <v>12501000</v>
+        <v>24688000</v>
       </c>
       <c r="J3" t="n">
-        <v>344678000</v>
+        <v>349926000</v>
       </c>
       <c r="K3" t="n">
-        <v>344678000</v>
+        <v>349926000</v>
       </c>
       <c r="L3" t="n">
-        <v>344678000</v>
+        <v>349926000</v>
       </c>
       <c r="M3" t="n">
-        <v>344678000</v>
+        <v>349926000</v>
       </c>
       <c r="N3" t="n">
         <v>10050000</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>186440000</v>
+        <v>187371000</v>
       </c>
       <c r="Q3" t="n">
         <v>136524000</v>
@@ -1748,132 +1748,130 @@
         <v>3590000</v>
       </c>
       <c r="T3" t="n">
-        <v>132670000</v>
+        <v>231924000</v>
       </c>
       <c r="U3" t="n">
-        <v>3499000</v>
+        <v>21017000</v>
       </c>
       <c r="V3" t="n">
-        <v>412000</v>
+        <v>584000</v>
       </c>
       <c r="W3" t="n">
-        <v>3087000</v>
+        <v>8428000</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>12005000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>12005000</v>
       </c>
       <c r="Z3" t="n">
-        <v>129171000</v>
+        <v>210907000</v>
       </c>
       <c r="AA3" t="n">
-        <v>33887000</v>
+        <v>48438000</v>
       </c>
       <c r="AB3" t="n">
-        <v>12501000</v>
+        <v>12683000</v>
       </c>
       <c r="AC3" t="n">
-        <v>21386000</v>
+        <v>35755000</v>
       </c>
       <c r="AD3" t="n">
-        <v>54374000</v>
+        <v>86604000</v>
       </c>
       <c r="AE3" t="n">
-        <v>2621000</v>
+        <v>1132000</v>
       </c>
       <c r="AF3" t="n">
-        <v>8898000</v>
+        <v>5746000</v>
       </c>
       <c r="AG3" t="n">
-        <v>42855000</v>
+        <v>79726000</v>
       </c>
       <c r="AH3" t="n">
-        <v>477348000</v>
+        <v>581850000</v>
       </c>
       <c r="AI3" t="n">
-        <v>153324000</v>
+        <v>171106000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>212000</v>
+        <v>181000</v>
       </c>
       <c r="AK3" t="n">
-        <v>2364000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
+        <v>1848000</v>
+      </c>
+      <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
-        <v>150748000</v>
+        <v>169077000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-56924000</v>
+        <v>-43541000</v>
       </c>
       <c r="AO3" t="n">
-        <v>207672000</v>
+        <v>212618000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1970000</v>
+        <v>3963000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>37236000</v>
+        <v>32108000</v>
       </c>
       <c r="AR3" t="n">
-        <v>59948000</v>
+        <v>56559000</v>
       </c>
       <c r="AS3" t="n">
-        <v>108518000</v>
+        <v>119988000</v>
       </c>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>324024000</v>
+        <v>410744000</v>
       </c>
       <c r="AV3" t="n">
-        <v>88000</v>
+        <v>87000</v>
       </c>
       <c r="AW3" t="n">
-        <v>5285000</v>
+        <v>8741000</v>
       </c>
       <c r="AX3" t="n">
-        <v>60100000</v>
+        <v>146623000</v>
       </c>
       <c r="AY3" t="n">
-        <v>17599000</v>
+        <v>47531000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>10715000</v>
+        <v>26234000</v>
       </c>
       <c r="BA3" t="n">
-        <v>31786000</v>
+        <v>72858000</v>
       </c>
       <c r="BB3" t="n">
-        <v>3300000</v>
+        <v>7181000</v>
       </c>
       <c r="BC3" t="n">
-        <v>61000</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>67471000</v>
+        <v>99192000</v>
       </c>
       <c r="BE3" t="n">
-        <v>-431000</v>
+        <v>-1125000</v>
       </c>
       <c r="BF3" t="n">
-        <v>67471000</v>
+        <v>99192000</v>
       </c>
       <c r="BG3" t="n">
-        <v>187719000</v>
+        <v>148920000</v>
       </c>
       <c r="BH3" t="n">
-        <v>187719000</v>
+        <v>148920000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>359000000</v>
@@ -1882,41 +1880,41 @@
         <v>359000000</v>
       </c>
       <c r="D4" t="n">
-        <v>60443000</v>
+        <v>33887000</v>
       </c>
       <c r="E4" t="n">
-        <v>349926000</v>
+        <v>344678000</v>
       </c>
       <c r="F4" t="n">
-        <v>385681000</v>
+        <v>366064000</v>
       </c>
       <c r="G4" t="n">
-        <v>199837000</v>
+        <v>194853000</v>
       </c>
       <c r="H4" t="n">
-        <v>349926000</v>
+        <v>344678000</v>
       </c>
       <c r="I4" t="n">
-        <v>24688000</v>
+        <v>12501000</v>
       </c>
       <c r="J4" t="n">
-        <v>349926000</v>
+        <v>344678000</v>
       </c>
       <c r="K4" t="n">
-        <v>349926000</v>
+        <v>344678000</v>
       </c>
       <c r="L4" t="n">
-        <v>349926000</v>
+        <v>344678000</v>
       </c>
       <c r="M4" t="n">
-        <v>349926000</v>
+        <v>344678000</v>
       </c>
       <c r="N4" t="n">
         <v>10050000</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>187371000</v>
+        <v>186440000</v>
       </c>
       <c r="Q4" t="n">
         <v>136524000</v>
@@ -1928,130 +1926,132 @@
         <v>3590000</v>
       </c>
       <c r="T4" t="n">
-        <v>231924000</v>
+        <v>132670000</v>
       </c>
       <c r="U4" t="n">
-        <v>21017000</v>
+        <v>3499000</v>
       </c>
       <c r="V4" t="n">
-        <v>584000</v>
+        <v>412000</v>
       </c>
       <c r="W4" t="n">
-        <v>8428000</v>
+        <v>3087000</v>
       </c>
       <c r="X4" t="n">
-        <v>12005000</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>12005000</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>210907000</v>
+        <v>129171000</v>
       </c>
       <c r="AA4" t="n">
-        <v>48438000</v>
+        <v>33887000</v>
       </c>
       <c r="AB4" t="n">
-        <v>12683000</v>
+        <v>12501000</v>
       </c>
       <c r="AC4" t="n">
-        <v>35755000</v>
+        <v>21386000</v>
       </c>
       <c r="AD4" t="n">
-        <v>86604000</v>
+        <v>54374000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1132000</v>
+        <v>2621000</v>
       </c>
       <c r="AF4" t="n">
-        <v>5746000</v>
+        <v>8898000</v>
       </c>
       <c r="AG4" t="n">
-        <v>79726000</v>
+        <v>42855000</v>
       </c>
       <c r="AH4" t="n">
-        <v>581850000</v>
+        <v>477348000</v>
       </c>
       <c r="AI4" t="n">
-        <v>171106000</v>
+        <v>153324000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>181000</v>
+        <v>212000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1848000</v>
-      </c>
-      <c r="AL4" t="inlineStr"/>
+        <v>2364000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
       <c r="AM4" t="n">
-        <v>169077000</v>
+        <v>150748000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-43541000</v>
+        <v>-56924000</v>
       </c>
       <c r="AO4" t="n">
-        <v>212618000</v>
+        <v>207672000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3963000</v>
+        <v>1970000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>32108000</v>
+        <v>37236000</v>
       </c>
       <c r="AR4" t="n">
-        <v>56559000</v>
+        <v>59948000</v>
       </c>
       <c r="AS4" t="n">
-        <v>119988000</v>
+        <v>108518000</v>
       </c>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>410744000</v>
+        <v>324024000</v>
       </c>
       <c r="AV4" t="n">
-        <v>87000</v>
+        <v>88000</v>
       </c>
       <c r="AW4" t="n">
-        <v>8741000</v>
+        <v>5285000</v>
       </c>
       <c r="AX4" t="n">
-        <v>146623000</v>
+        <v>60100000</v>
       </c>
       <c r="AY4" t="n">
-        <v>47531000</v>
+        <v>17599000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>26234000</v>
+        <v>10715000</v>
       </c>
       <c r="BA4" t="n">
-        <v>72858000</v>
+        <v>31786000</v>
       </c>
       <c r="BB4" t="n">
-        <v>7181000</v>
+        <v>3300000</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>61000</v>
       </c>
       <c r="BD4" t="n">
-        <v>99192000</v>
+        <v>67471000</v>
       </c>
       <c r="BE4" t="n">
-        <v>-1125000</v>
+        <v>-431000</v>
       </c>
       <c r="BF4" t="n">
-        <v>99192000</v>
+        <v>67471000</v>
       </c>
       <c r="BG4" t="n">
-        <v>148920000</v>
+        <v>187719000</v>
       </c>
       <c r="BH4" t="n">
-        <v>148920000</v>
+        <v>187719000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>359000000</v>
@@ -2060,43 +2060,41 @@
         <v>359000000</v>
       </c>
       <c r="D5" t="n">
-        <v>115317000</v>
+        <v>87726000</v>
       </c>
       <c r="E5" t="n">
-        <v>332186000</v>
+        <v>355042000</v>
       </c>
       <c r="F5" t="n">
-        <v>412330000</v>
+        <v>395017000</v>
       </c>
       <c r="G5" t="n">
-        <v>253231000</v>
+        <v>170577000</v>
       </c>
       <c r="H5" t="n">
-        <v>332186000</v>
+        <v>355042000</v>
       </c>
       <c r="I5" t="n">
-        <v>35173000</v>
+        <v>47751000</v>
       </c>
       <c r="J5" t="n">
-        <v>332186000</v>
+        <v>355042000</v>
       </c>
       <c r="K5" t="n">
-        <v>332186000</v>
+        <v>355042000</v>
       </c>
       <c r="L5" t="n">
-        <v>332186000</v>
+        <v>355042000</v>
       </c>
       <c r="M5" t="n">
-        <v>332186000</v>
+        <v>355042000</v>
       </c>
       <c r="N5" t="n">
         <v>10050000</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>163967000</v>
+        <v>200351000</v>
       </c>
       <c r="Q5" t="n">
         <v>136524000</v>
@@ -2108,125 +2106,127 @@
         <v>3590000</v>
       </c>
       <c r="T5" t="n">
-        <v>276291000</v>
+        <v>199414000</v>
       </c>
       <c r="U5" t="n">
-        <v>28006000</v>
+        <v>33802000</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>220000</v>
       </c>
       <c r="W5" t="n">
-        <v>5906000</v>
+        <v>1999000</v>
       </c>
       <c r="X5" t="n">
-        <v>22100000</v>
+        <v>31583000</v>
       </c>
       <c r="Y5" t="n">
-        <v>22100000</v>
+        <v>31583000</v>
       </c>
       <c r="Z5" t="n">
-        <v>248285000</v>
+        <v>165612000</v>
       </c>
       <c r="AA5" t="n">
-        <v>93217000</v>
+        <v>56143000</v>
       </c>
       <c r="AB5" t="n">
-        <v>13073000</v>
+        <v>16168000</v>
       </c>
       <c r="AC5" t="n">
-        <v>80144000</v>
+        <v>39975000</v>
       </c>
       <c r="AD5" t="n">
-        <v>94697000</v>
+        <v>61707000</v>
       </c>
       <c r="AE5" t="n">
-        <v>653000</v>
+        <v>1649000</v>
       </c>
       <c r="AF5" t="n">
-        <v>3471000</v>
+        <v>1604000</v>
       </c>
       <c r="AG5" t="n">
-        <v>90573000</v>
+        <v>58454000</v>
       </c>
       <c r="AH5" t="n">
-        <v>608477000</v>
+        <v>554456000</v>
       </c>
       <c r="AI5" t="n">
-        <v>106961000</v>
+        <v>218267000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>65000</v>
+        <v>206000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1138000</v>
-      </c>
-      <c r="AL5" t="inlineStr"/>
+        <v>3337000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2200000</v>
+      </c>
       <c r="AM5" t="n">
-        <v>105758000</v>
+        <v>212524000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-35670000</v>
+        <v>-69650000</v>
       </c>
       <c r="AO5" t="n">
-        <v>141428000</v>
+        <v>282174000</v>
       </c>
       <c r="AP5" t="n">
-        <v>18697000</v>
+        <v>11384000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>30783000</v>
+        <v>43983000</v>
       </c>
       <c r="AR5" t="n">
-        <v>49609000</v>
+        <v>65226000</v>
       </c>
       <c r="AS5" t="n">
-        <v>42339000</v>
+        <v>161581000</v>
       </c>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>501516000</v>
+        <v>336189000</v>
       </c>
       <c r="AV5" t="n">
-        <v>88000</v>
+        <v>820000</v>
       </c>
       <c r="AW5" t="n">
-        <v>27011000</v>
+        <v>17754000</v>
       </c>
       <c r="AX5" t="n">
-        <v>206732000</v>
+        <v>100128000</v>
       </c>
       <c r="AY5" t="n">
-        <v>46071000</v>
+        <v>48285000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>42421000</v>
+        <v>17213000</v>
       </c>
       <c r="BA5" t="n">
-        <v>118240000</v>
+        <v>34630000</v>
       </c>
       <c r="BB5" t="n">
-        <v>26910000</v>
+        <v>5736000</v>
       </c>
       <c r="BC5" t="n">
-        <v>3683000</v>
+        <v>153000</v>
       </c>
       <c r="BD5" t="n">
-        <v>119180000</v>
+        <v>135704000</v>
       </c>
       <c r="BE5" t="n">
-        <v>-101000</v>
+        <v>-3635000</v>
       </c>
       <c r="BF5" t="n">
-        <v>119180000</v>
+        <v>135704000</v>
       </c>
       <c r="BG5" t="n">
-        <v>144923000</v>
+        <v>75894000</v>
       </c>
       <c r="BH5" t="n">
-        <v>144923000</v>
+        <v>75894000</v>
       </c>
     </row>
   </sheetData>
@@ -2447,470 +2447,470 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-22135000</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>-22784000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
       <c r="D2" t="n">
-        <v>-53363000</v>
+        <v>-68979000</v>
       </c>
       <c r="E2" t="n">
-        <v>71952000</v>
+        <v>109518000</v>
       </c>
       <c r="F2" t="n">
-        <v>-45245000</v>
+        <v>-39607000</v>
       </c>
       <c r="G2" t="n">
-        <v>75894000</v>
+        <v>144923000</v>
       </c>
       <c r="H2" t="n">
-        <v>187719000</v>
+        <v>223945000</v>
       </c>
       <c r="I2" t="n">
-        <v>-308000</v>
+        <v>1341000</v>
       </c>
       <c r="J2" t="n">
-        <v>-111517000</v>
+        <v>-80363000</v>
       </c>
       <c r="K2" t="n">
-        <v>-91199000</v>
+        <v>-59847000</v>
       </c>
       <c r="L2" t="n">
-        <v>-2312000</v>
+        <v>-788000</v>
       </c>
       <c r="M2" t="n">
-        <v>-93699000</v>
+        <v>-86878000</v>
       </c>
       <c r="N2" t="n">
-        <v>-93699000</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+        <v>-86878000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q2" t="n">
-        <v>18589000</v>
+        <v>40539000</v>
       </c>
       <c r="R2" t="n">
-        <v>18589000</v>
+        <v>40539000</v>
       </c>
       <c r="S2" t="n">
-        <v>-53363000</v>
+        <v>-68979000</v>
       </c>
       <c r="T2" t="n">
-        <v>71952000</v>
+        <v>109518000</v>
       </c>
       <c r="U2" t="n">
-        <v>-43428000</v>
+        <v>-37339000</v>
       </c>
       <c r="V2" t="n">
-        <v>-745000</v>
+        <v>1032000</v>
       </c>
       <c r="W2" t="n">
-        <v>4743000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-2211000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-2211000</v>
-      </c>
+        <v>1236000</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>-45215000</v>
+        <v>-39607000</v>
       </c>
       <c r="AA2" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-45245000</v>
+        <v>-39607000</v>
       </c>
       <c r="AC2" t="n">
-        <v>23110000</v>
+        <v>16823000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-32190000</v>
+        <v>-21266000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-99916000</v>
+        <v>-111684000</v>
       </c>
       <c r="AF2" t="n">
-        <v>22791000</v>
+        <v>42235000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-18550000</v>
+        <v>-5914000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-35924000</v>
+        <v>-120120000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-68233000</v>
+        <v>-27885000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-2431000</v>
+        <v>-396000</v>
       </c>
       <c r="AK2" t="n">
-        <v>31042000</v>
+        <v>25846000</v>
       </c>
       <c r="AL2" t="n">
-        <v>31042000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>11000</v>
-      </c>
+        <v>25846000</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
-        <v>42000</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>130417000</v>
+        <v>125864000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>183129000</v>
+        <v>148311000</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>-18846000</v>
+        <v>-234152000</v>
       </c>
       <c r="E3" t="n">
-        <v>4477000</v>
+        <v>189763000</v>
       </c>
       <c r="F3" t="n">
-        <v>-13567000</v>
+        <v>-109337000</v>
       </c>
       <c r="G3" t="n">
-        <v>187719000</v>
+        <v>148920000</v>
       </c>
       <c r="H3" t="n">
-        <v>148920000</v>
+        <v>144923000</v>
       </c>
       <c r="I3" t="n">
-        <v>-491000</v>
+        <v>-2314000</v>
       </c>
       <c r="J3" t="n">
-        <v>39290000</v>
+        <v>6311000</v>
       </c>
       <c r="K3" t="n">
-        <v>-152000000</v>
+        <v>-157148000</v>
       </c>
       <c r="L3" t="n">
-        <v>-2587000</v>
+        <v>-4025000</v>
       </c>
       <c r="M3" t="n">
-        <v>-123137000</v>
+        <v>-96212000</v>
       </c>
       <c r="N3" t="n">
-        <v>-123137000</v>
+        <v>-96212000</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>-14369000</v>
+        <v>-44389000</v>
       </c>
       <c r="R3" t="n">
-        <v>-14369000</v>
+        <v>-44389000</v>
       </c>
       <c r="S3" t="n">
-        <v>-18846000</v>
+        <v>-234152000</v>
       </c>
       <c r="T3" t="n">
-        <v>4477000</v>
+        <v>189763000</v>
       </c>
       <c r="U3" t="n">
-        <v>-5406000</v>
+        <v>-94189000</v>
       </c>
       <c r="V3" t="n">
-        <v>-2000</v>
+        <v>-7000</v>
       </c>
       <c r="W3" t="n">
-        <v>6132000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
+        <v>877000</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>-11536000</v>
+        <v>-95059000</v>
       </c>
       <c r="AA3" t="n">
-        <v>2031000</v>
+        <v>14278000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-13567000</v>
+        <v>-109337000</v>
       </c>
       <c r="AC3" t="n">
-        <v>196696000</v>
+        <v>257648000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-27182000</v>
+        <v>-18074000</v>
       </c>
       <c r="AE3" t="n">
-        <v>37694000</v>
+        <v>80576000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-69354000</v>
+        <v>14728000</v>
       </c>
       <c r="AG3" t="n">
-        <v>7813000</v>
+        <v>7950000</v>
       </c>
       <c r="AH3" t="n">
-        <v>67529000</v>
+        <v>37978000</v>
       </c>
       <c r="AI3" t="n">
-        <v>31706000</v>
+        <v>19920000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-3545000</v>
+        <v>3091000</v>
       </c>
       <c r="AK3" t="n">
-        <v>28735000</v>
+        <v>27918000</v>
       </c>
       <c r="AL3" t="n">
-        <v>28735000</v>
+        <v>27918000</v>
       </c>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>15000</v>
+        <v>631000</v>
       </c>
       <c r="AO3" t="n">
-        <v>146760000</v>
+        <v>161031000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>148311000</v>
+        <v>183129000</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-234152000</v>
+        <v>-18846000</v>
       </c>
       <c r="E4" t="n">
-        <v>189763000</v>
+        <v>4477000</v>
       </c>
       <c r="F4" t="n">
-        <v>-109337000</v>
+        <v>-13567000</v>
       </c>
       <c r="G4" t="n">
+        <v>187719000</v>
+      </c>
+      <c r="H4" t="n">
         <v>148920000</v>
       </c>
-      <c r="H4" t="n">
-        <v>144923000</v>
-      </c>
       <c r="I4" t="n">
-        <v>-2314000</v>
+        <v>-491000</v>
       </c>
       <c r="J4" t="n">
-        <v>6311000</v>
+        <v>39290000</v>
       </c>
       <c r="K4" t="n">
-        <v>-157148000</v>
+        <v>-152000000</v>
       </c>
       <c r="L4" t="n">
-        <v>-4025000</v>
+        <v>-2587000</v>
       </c>
       <c r="M4" t="n">
-        <v>-96212000</v>
+        <v>-123137000</v>
       </c>
       <c r="N4" t="n">
-        <v>-96212000</v>
+        <v>-123137000</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>-44389000</v>
+        <v>-14369000</v>
       </c>
       <c r="R4" t="n">
-        <v>-44389000</v>
+        <v>-14369000</v>
       </c>
       <c r="S4" t="n">
-        <v>-234152000</v>
+        <v>-18846000</v>
       </c>
       <c r="T4" t="n">
-        <v>189763000</v>
+        <v>4477000</v>
       </c>
       <c r="U4" t="n">
-        <v>-94189000</v>
+        <v>-5406000</v>
       </c>
       <c r="V4" t="n">
-        <v>-7000</v>
+        <v>-2000</v>
       </c>
       <c r="W4" t="n">
-        <v>877000</v>
-      </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
+        <v>6132000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z4" t="n">
-        <v>-95059000</v>
+        <v>-11536000</v>
       </c>
       <c r="AA4" t="n">
-        <v>14278000</v>
+        <v>2031000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-109337000</v>
+        <v>-13567000</v>
       </c>
       <c r="AC4" t="n">
-        <v>257648000</v>
+        <v>196696000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-18074000</v>
+        <v>-27182000</v>
       </c>
       <c r="AE4" t="n">
-        <v>80576000</v>
+        <v>37694000</v>
       </c>
       <c r="AF4" t="n">
-        <v>14728000</v>
+        <v>-69354000</v>
       </c>
       <c r="AG4" t="n">
-        <v>7950000</v>
+        <v>7813000</v>
       </c>
       <c r="AH4" t="n">
-        <v>37978000</v>
+        <v>67529000</v>
       </c>
       <c r="AI4" t="n">
-        <v>19920000</v>
+        <v>31706000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3091000</v>
+        <v>-3545000</v>
       </c>
       <c r="AK4" t="n">
-        <v>27918000</v>
+        <v>28735000</v>
       </c>
       <c r="AL4" t="n">
-        <v>27918000</v>
+        <v>28735000</v>
       </c>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>631000</v>
+        <v>15000</v>
       </c>
       <c r="AO4" t="n">
-        <v>161031000</v>
+        <v>146760000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-22784000</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
+        <v>-22135000</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>-68979000</v>
+        <v>-53363000</v>
       </c>
       <c r="E5" t="n">
-        <v>109518000</v>
+        <v>71952000</v>
       </c>
       <c r="F5" t="n">
-        <v>-39607000</v>
+        <v>-45245000</v>
       </c>
       <c r="G5" t="n">
-        <v>144923000</v>
+        <v>75894000</v>
       </c>
       <c r="H5" t="n">
-        <v>223945000</v>
+        <v>187719000</v>
       </c>
       <c r="I5" t="n">
-        <v>1341000</v>
+        <v>-308000</v>
       </c>
       <c r="J5" t="n">
-        <v>-80363000</v>
+        <v>-111517000</v>
       </c>
       <c r="K5" t="n">
-        <v>-59847000</v>
+        <v>-91199000</v>
       </c>
       <c r="L5" t="n">
-        <v>-788000</v>
+        <v>-2312000</v>
       </c>
       <c r="M5" t="n">
-        <v>-86878000</v>
+        <v>-93699000</v>
       </c>
       <c r="N5" t="n">
-        <v>-86878000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
+        <v>-93699000</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>40539000</v>
+        <v>18589000</v>
       </c>
       <c r="R5" t="n">
-        <v>40539000</v>
+        <v>18589000</v>
       </c>
       <c r="S5" t="n">
-        <v>-68979000</v>
+        <v>-53363000</v>
       </c>
       <c r="T5" t="n">
-        <v>109518000</v>
+        <v>71952000</v>
       </c>
       <c r="U5" t="n">
-        <v>-37339000</v>
+        <v>-43428000</v>
       </c>
       <c r="V5" t="n">
-        <v>1032000</v>
+        <v>-745000</v>
       </c>
       <c r="W5" t="n">
-        <v>1236000</v>
-      </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
+        <v>4743000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-2211000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-2211000</v>
+      </c>
       <c r="Z5" t="n">
-        <v>-39607000</v>
+        <v>-45215000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-39607000</v>
+        <v>-45245000</v>
       </c>
       <c r="AC5" t="n">
-        <v>16823000</v>
+        <v>23110000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-21266000</v>
+        <v>-32190000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-111684000</v>
+        <v>-99916000</v>
       </c>
       <c r="AF5" t="n">
-        <v>42235000</v>
+        <v>22791000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-5914000</v>
+        <v>-18550000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-120120000</v>
+        <v>-35924000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-27885000</v>
+        <v>-68233000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-396000</v>
+        <v>-2431000</v>
       </c>
       <c r="AK5" t="n">
-        <v>25846000</v>
+        <v>31042000</v>
       </c>
       <c r="AL5" t="n">
-        <v>25846000</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
+        <v>31042000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>11000</v>
+      </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>42000</v>
       </c>
       <c r="AO5" t="n">
-        <v>125864000</v>
+        <v>130417000</v>
       </c>
     </row>
   </sheetData>
@@ -3460,182 +3460,182 @@
       </c>
       <c r="DC1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
         <is>
           <t>shortName</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
         </is>
       </c>
       <c r="EM1" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Dr. Kam Kwong  Chan', 'age': 66, 'title': 'Co-Founder &amp; Non-Executive Chairman', 'yearBorn': 1959, 'fiscalYear': 2025, 'totalPay': 4584000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wai Ming  Chan', 'age': 56, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1969, 'fiscalYear': 2025, 'totalPay': 1999000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yuk Sim  Cheng', 'age': 67, 'title': 'Co-founder &amp; Non-Executive Director', 'yearBorn': 1958, 'fiscalYear': 2025, 'totalPay': 4139000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wai Kwong  Chiu', 'age': 60, 'title': 'Finance Director', 'yearBorn': 1965, 'fiscalYear': 2025, 'totalPay': 1713000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kwok Wai  Yu', 'age': 48, 'title': 'Marketing Director &amp; Executive Director', 'yearBorn': 1977, 'fiscalYear': 2025, 'totalPay': 1201000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Mei Wah  Tang', 'age': 50, 'title': 'MD &amp; Executive Director', 'yearBorn': 1975, 'fiscalYear': 2025, 'totalPay': 1255000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ming Yiu  Tung', 'age': 40, 'title': 'Accounting Director, Company Secretary &amp; Executive Director', 'yearBorn': 1985, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kwok Ho  Lee', 'age': 42, 'title': 'Sales Director', 'yearBorn': 1983, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Hok Keung  Luk', 'title': 'Executive Director', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Pak Man  Lee', 'title': 'Executive Director', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Dr. Kam Kwong  Chan', 'age': 66, 'title': 'Co-Founder &amp; Non-Executive Chairman', 'yearBorn': 1959, 'fiscalYear': 2025, 'totalPay': 4584000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wai Ming  Chan', 'age': 56, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1969, 'fiscalYear': 2025, 'totalPay': 1999000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yuk Sim  Cheng', 'age': 67, 'title': 'Co-founder &amp; Non-Executive Director', 'yearBorn': 1958, 'fiscalYear': 2025, 'totalPay': 4139000, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -3743,34 +3743,34 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>1.525</v>
+        <v>1.54</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W2" t="n">
         <v>1.5</v>
       </c>
       <c r="X2" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.525</v>
+        <v>1.54</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AA2" t="n">
         <v>1.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC2" t="n">
         <v>0.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>9.06</v>
+        <v>9.67</v>
       </c>
       <c r="AE2" t="n">
         <v>1780012800</v>
@@ -3782,43 +3782,43 @@
         <v>11.63</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.026</v>
+        <v>0.036</v>
       </c>
       <c r="AI2" t="n">
-        <v>9.411765000000001</v>
+        <v>8.823529000000001</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18000</v>
+        <v>30000</v>
       </c>
       <c r="AK2" t="n">
-        <v>18000</v>
+        <v>30000</v>
       </c>
       <c r="AL2" t="n">
-        <v>19433</v>
+        <v>19220</v>
       </c>
       <c r="AM2" t="n">
-        <v>2200</v>
+        <v>6200</v>
       </c>
       <c r="AN2" t="n">
-        <v>2200</v>
+        <v>6200</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ2" t="n">
-        <v>574400000</v>
+        <v>538499968</v>
       </c>
       <c r="AR2" t="n">
-        <v>574400000</v>
+        <v>639020000</v>
       </c>
       <c r="AS2" t="n">
         <v>1.41</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AU2" t="n">
         <v>3.48</v>
@@ -3827,19 +3827,19 @@
         <v>0.43</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.8539423</v>
+        <v>0.8005708499999999</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.599</v>
+        <v>1.5766</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.73325</v>
+        <v>1.70955</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.145</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.09508195999999999</v>
+        <v>0.09415584</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -3850,19 +3850,19 @@
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>529847008</v>
+        <v>493947008</v>
       </c>
       <c r="BE2" t="n">
         <v>0.09304</v>
       </c>
       <c r="BF2" t="n">
-        <v>67194030</v>
+        <v>62193160</v>
       </c>
       <c r="BG2" t="n">
         <v>359000000</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.8128300000000001</v>
+        <v>0.82676005</v>
       </c>
       <c r="BI2" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
         <v>0.946</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.691332</v>
+        <v>1.5856237</v>
       </c>
       <c r="BM2" t="n">
         <v>1767139200</v>
@@ -3895,16 +3895,16 @@
         <v>0.17</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.788</v>
+        <v>0.734</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.197</v>
+        <v>5.777</v>
       </c>
       <c r="BU2" t="n">
-        <v>-0.3333333</v>
+        <v>-0.35622317</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BW2" t="n">
         <v>0.075</v>
@@ -3918,7 +3918,7 @@
         </is>
       </c>
       <c r="BZ2" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
@@ -4020,135 +4020,135 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DC2" t="b">
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DD2" t="n">
+        <v>1781769353</v>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>finmb_638837417</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DI2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DK2" t="b">
         <v>0</v>
       </c>
-      <c r="DD2" t="n">
+      <c r="DL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DM2" t="n">
         <v>1571967000000</v>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DN2" t="n">
+        <v>-0.03999996</v>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>1.5 - 1.52</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DQ2" t="n">
+        <v>19220</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0.09000002999999999</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>0.06382981</v>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>1.41 - 2.37</t>
+        </is>
+      </c>
+      <c r="DU2" t="n">
+        <v>-0.8699999</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-0.3670886</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>-35.62232</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>1742210083</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>1742210083</v>
+      </c>
+      <c r="DZ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>-2.5974002</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>-0.076599956</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.048585538</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-0.20955002</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.122576125</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
         <is>
           <t>TOWNRAY HLDGS</t>
         </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DG2" t="n">
-        <v>1780041263</v>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>finmb_638837417</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="DP2" t="n">
-        <v>4.918036</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0.07500005</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>1.5 - 1.5</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DT2" t="n">
-        <v>19433</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0.19000006</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>0.13475181</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>1.41 - 2.4</t>
-        </is>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.8000001</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.33333334</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-33.333332</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>1742210083</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>1742210083</v>
-      </c>
-      <c r="EC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>0.0010000467</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>0.0006254201</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.13325</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-0.07687869999999999</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EL2" t="b">
-        <v>0</v>
       </c>
       <c r="EM2" t="inlineStr">
         <is>
